--- a/测试用例.xlsx
+++ b/测试用例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="2"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="测试用例" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>用例编号</t>
   </si>
@@ -159,18 +159,6 @@
   </si>
   <si>
     <t>001BUG.jpeg</t>
-  </si>
-  <si>
-    <t>级别</t>
-  </si>
-  <si>
-    <t>名称</t>
-  </si>
-  <si>
-    <t>定义</t>
-  </si>
-  <si>
-    <t>示例</t>
   </si>
   <si>
     <r>
@@ -284,63 +272,6 @@
       </rPr>
       <t>，但钱已扣。</t>
     </r>
-  </si>
-  <si>
-    <t>S1</t>
-  </si>
-  <si>
-    <t>致命 Blocker</t>
-  </si>
-  <si>
-    <t>系统崩溃、数据丢失、核心功能完全不可用</t>
-  </si>
-  <si>
-    <t>支付后扣款但订单未生成</t>
-  </si>
-  <si>
-    <t>S2</t>
-  </si>
-  <si>
-    <t>严重 Critical</t>
-  </si>
-  <si>
-    <t>核心功能部分不可用、无替代方案</t>
-  </si>
-  <si>
-    <t>登录功能偶尔失败</t>
-  </si>
-  <si>
-    <t>S3</t>
-  </si>
-  <si>
-    <t>一般 Major</t>
-  </si>
-  <si>
-    <t>功能可用但有明显问题、有替代方案</t>
-  </si>
-  <si>
-    <t>导出报表格式错乱</t>
-  </si>
-  <si>
-    <t>轻微 Minor</t>
-  </si>
-  <si>
-    <t>界面/提示等不影响功能使用</t>
-  </si>
-  <si>
-    <t>按钮颜色与设计稿不一致</t>
-  </si>
-  <si>
-    <t>S5</t>
-  </si>
-  <si>
-    <t>建议 Suggestion</t>
-  </si>
-  <si>
-    <t>改进建议</t>
-  </si>
-  <si>
-    <t>"建议把按钮做大一些"</t>
   </si>
 </sst>
 </file>
@@ -1041,7 +972,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1064,6 +995,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1404,84 +1338,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.1111111111111" style="9" customWidth="1"/>
-    <col min="2" max="2" width="9.66666666666667" style="9" customWidth="1"/>
-    <col min="3" max="3" width="36.4444444444444" style="9" customWidth="1"/>
-    <col min="4" max="4" width="44.7037037037037" style="9" customWidth="1"/>
-    <col min="5" max="5" width="22" style="9" customWidth="1"/>
-    <col min="6" max="6" width="19.6666666666667" style="9" customWidth="1"/>
-    <col min="7" max="7" width="26.7962962962963" style="9" customWidth="1"/>
-    <col min="8" max="8" width="21.8333333333333" style="9" customWidth="1"/>
-    <col min="9" max="9" width="9" style="9"/>
-    <col min="10" max="10" width="36" style="9" customWidth="1"/>
-    <col min="11" max="12" width="9" style="9"/>
-    <col min="13" max="13" width="53.5555555555556" style="9" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="14.1111111111111" style="10" customWidth="1"/>
+    <col min="2" max="2" width="9.66666666666667" style="10" customWidth="1"/>
+    <col min="3" max="3" width="36.4444444444444" style="10" customWidth="1"/>
+    <col min="4" max="4" width="44.7037037037037" style="10" customWidth="1"/>
+    <col min="5" max="5" width="22" style="10" customWidth="1"/>
+    <col min="6" max="6" width="19.6666666666667" style="10" customWidth="1"/>
+    <col min="7" max="7" width="26.7962962962963" style="10" customWidth="1"/>
+    <col min="8" max="8" width="21.8333333333333" style="10" customWidth="1"/>
+    <col min="9" max="9" width="9" style="10"/>
+    <col min="10" max="10" width="36" style="10" customWidth="1"/>
+    <col min="11" max="12" width="9" style="10"/>
+    <col min="13" max="13" width="53.5555555555556" style="10" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.6" spans="1:10">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="12"/>
+      <c r="I1" s="13"/>
     </row>
     <row r="2" ht="57.6" spans="1:10">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="14" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="H6" s="13"/>
-    </row>
-    <row r="16" ht="172.8" spans="1:10">
-      <c r="J16" s="13" t="s">
+      <c r="H6" s="14"/>
+    </row>
+    <row r="15" ht="15.15"/>
+    <row r="16" ht="173.55" spans="1:10">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="J16" s="14" t="s">
         <v>16</v>
       </c>
+    </row>
+    <row r="17" ht="16.35" spans="1:4">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+    </row>
+    <row r="18" ht="16.35" spans="1:4">
+      <c r="A18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" ht="16.35" spans="1:4">
+      <c r="A19" s="4"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" ht="16.35" spans="1:4">
+      <c r="A20" s="6"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" ht="16.35" spans="1:4">
+      <c r="A21" s="4"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1500,7 +1469,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" spans="1:12">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B1" t="s">
@@ -1599,7 +1568,7 @@
       <c r="E2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="16" t="s">
         <v>32</v>
       </c>
       <c r="G2" s="1" t="s">
@@ -1617,91 +1586,43 @@
     </row>
     <row r="4" ht="15.15"/>
     <row r="5" ht="97" customHeight="1" spans="1:14">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="N5" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="6" ht="16.35" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>45</v>
-      </c>
+      <c r="A6" s="4"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" ht="16.35" spans="1:14">
-      <c r="A7" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>49</v>
-      </c>
+      <c r="A7" s="6"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
     </row>
     <row r="8" ht="16.35" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="A8" s="4"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" ht="16.35" spans="1:14">
-      <c r="A9" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>56</v>
-      </c>
+      <c r="A9" s="6"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
     </row>
     <row r="10" ht="16.35" spans="1:14">
-      <c r="A10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>60</v>
-      </c>
+      <c r="A10" s="4"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
